--- a/testdata/realdata/machine_rooms.xlsx
+++ b/testdata/realdata/machine_rooms.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E84"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,6 +442,11 @@
           <t>区县</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -465,6 +470,11 @@
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -492,6 +502,11 @@
           <t>讷河</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -515,6 +530,11 @@
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -542,6 +562,11 @@
           <t>大同</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -565,6 +590,11 @@
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -592,6 +622,11 @@
           <t>巴彦</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -615,6 +650,11 @@
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -638,6 +678,11 @@
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -665,6 +710,11 @@
           <t>方正</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -692,6 +742,11 @@
           <t>甘南</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -715,6 +770,11 @@
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -742,6 +802,11 @@
           <t>呼兰</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -765,6 +830,11 @@
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -792,6 +862,11 @@
           <t>林口</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -819,6 +894,11 @@
           <t>漠河</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -846,6 +926,11 @@
           <t>木兰</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -873,6 +958,11 @@
           <t>青冈</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -900,6 +990,11 @@
           <t>庆安</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -923,6 +1018,11 @@
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -946,6 +1046,11 @@
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -973,6 +1078,11 @@
           <t>汤原</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -996,6 +1106,11 @@
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1023,6 +1138,11 @@
           <t>绥棱</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1050,6 +1170,11 @@
           <t>塔河</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1077,6 +1202,11 @@
           <t>望奎</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1104,6 +1234,11 @@
           <t>通河</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1127,6 +1262,11 @@
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1154,6 +1294,11 @@
           <t>延寿</t>
         </is>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1177,6 +1322,11 @@
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1204,6 +1354,11 @@
           <t>鄂伦春自治旗</t>
         </is>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1231,6 +1386,11 @@
           <t>城子河</t>
         </is>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1258,6 +1418,11 @@
           <t>爱民</t>
         </is>
       </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1285,6 +1450,11 @@
           <t>道里</t>
         </is>
       </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1312,6 +1482,11 @@
           <t>松北</t>
         </is>
       </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1339,6 +1514,11 @@
           <t>香坊</t>
         </is>
       </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1366,6 +1546,11 @@
           <t>南岗</t>
         </is>
       </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1393,6 +1578,11 @@
           <t>道外</t>
         </is>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1420,6 +1610,11 @@
           <t>西安</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1447,6 +1642,11 @@
           <t>东安</t>
         </is>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1474,6 +1674,11 @@
           <t>乌翠</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1501,6 +1706,11 @@
           <t>龙沙</t>
         </is>
       </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1528,6 +1738,11 @@
           <t>新兴</t>
         </is>
       </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1551,6 +1766,11 @@
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1574,6 +1794,11 @@
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1597,6 +1822,11 @@
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1624,6 +1854,11 @@
           <t>富裕</t>
         </is>
       </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1647,6 +1882,11 @@
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1674,6 +1914,11 @@
           <t>依安</t>
         </is>
       </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1701,6 +1946,11 @@
           <t>铁力</t>
         </is>
       </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1724,6 +1974,11 @@
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1747,6 +2002,11 @@
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1770,6 +2030,11 @@
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1793,6 +2058,11 @@
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1820,6 +2090,11 @@
           <t>阿城</t>
         </is>
       </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1847,6 +2122,11 @@
           <t>伊春</t>
         </is>
       </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1870,6 +2150,11 @@
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1893,6 +2178,11 @@
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1916,6 +2206,11 @@
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1939,6 +2234,11 @@
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1966,6 +2266,11 @@
           <t>安达</t>
         </is>
       </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1993,6 +2298,11 @@
           <t>肇东</t>
         </is>
       </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2020,6 +2330,11 @@
           <t>兰西</t>
         </is>
       </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2047,6 +2362,11 @@
           <t>铁锋</t>
         </is>
       </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2074,6 +2394,11 @@
           <t>昂昂溪</t>
         </is>
       </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2101,6 +2426,11 @@
           <t>梅里斯达斡尔族</t>
         </is>
       </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2128,6 +2458,11 @@
           <t>杜尔伯特蒙古族自治县 ᠳᠥᠷᠪᠡᠳ ᠮᠣᠩᠭᠣᠯ ᠥᠪᠡᠷᠲᠡᠭᠡᠨ ᠵᠠᠰᠠᠬᠤ ᠰᠢᠶᠠᠨ</t>
         </is>
       </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2155,6 +2490,11 @@
           <t>让胡路</t>
         </is>
       </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2182,6 +2522,11 @@
           <t>萨尔图</t>
         </is>
       </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2209,6 +2554,11 @@
           <t>肇源</t>
         </is>
       </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2236,6 +2586,11 @@
           <t>肇州</t>
         </is>
       </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2263,6 +2618,11 @@
           <t>平房</t>
         </is>
       </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2290,6 +2650,11 @@
           <t>尚志</t>
         </is>
       </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2317,6 +2682,11 @@
           <t>海林</t>
         </is>
       </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2344,6 +2714,11 @@
           <t>阳明</t>
         </is>
       </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2371,6 +2746,11 @@
           <t>穆棱</t>
         </is>
       </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2398,6 +2778,11 @@
           <t>麻山</t>
         </is>
       </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2425,6 +2810,11 @@
           <t>恒山</t>
         </is>
       </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2452,6 +2842,11 @@
           <t>岭东</t>
         </is>
       </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2479,6 +2874,11 @@
           <t>集贤</t>
         </is>
       </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2506,6 +2906,11 @@
           <t>郊</t>
         </is>
       </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2533,6 +2938,11 @@
           <t>勃利</t>
         </is>
       </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2556,6 +2966,11 @@
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2579,6 +2994,11 @@
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
